--- a/mau_tkb.xlsx
+++ b/mau_tkb.xlsx
@@ -1293,7 +1293,7 @@
       <c r="J5" s="91" t="n"/>
       <c r="K5" s="91" t="n"/>
     </row>
-    <row r="6" ht="12.75" customHeight="1" s="88">
+    <row r="6" s="88">
       <c r="A6" s="100" t="n"/>
       <c r="B6" s="101" t="n"/>
       <c r="C6" s="102" t="n"/>
@@ -2769,7 +2769,7 @@
     <mergeCell ref="C5:C6"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.95" right="0.7" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.95" right="0.7" top="0.35" bottom="0.35" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/mau_tkb.xlsx
+++ b/mau_tkb.xlsx
@@ -1992,7 +1992,7 @@
       <c r="J44" s="91" t="n"/>
       <c r="K44" s="91" t="n"/>
     </row>
-    <row r="45" ht="12.75" customHeight="1" s="88">
+    <row r="45" s="88">
       <c r="A45" s="174" t="n"/>
       <c r="B45" s="175" t="inlineStr">
         <is>
@@ -2741,7 +2741,8 @@
       <c r="K100" s="91" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
+    <mergeCell ref="B45:I45"/>
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="B38:B42"/>
